--- a/output/screener_output.xlsx
+++ b/output/screener_output.xlsx
@@ -442,12 +442,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
@@ -459,7 +459,7 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
@@ -578,7 +578,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -588,204 +588,1467 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.32776263242075</v>
+        <v>91.04945832404229</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>17.99027109750765</v>
+        <v>892.5683060109289</v>
       </c>
       <c r="F2" t="n">
-        <v>5.220349505440574</v>
+        <v>5640.87982832618</v>
       </c>
       <c r="G2" t="n">
-        <v>28.8880112339828</v>
+        <v>11.8527226285847</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>12547</v>
+        <v>9424</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.360467011220518</v>
+        <v>71.56520119992503</v>
       </c>
       <c r="J2" t="n">
-        <v>3.413207178663658</v>
+        <v>2.593730868127832</v>
       </c>
       <c r="K2" t="n">
-        <v>21.39660074377121</v>
+        <v>67.58091776468258</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>17.25086850260209</v>
-      </c>
-      <c r="M2" t="n">
-        <v>31.28635844345755</v>
+        <v>19.31335512580617</v>
       </c>
       <c r="N2" t="n">
-        <v>51.94877118224903</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>6.445624336310825</v>
+        <v>120.6925086746793</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.01857923497267759</v>
       </c>
       <c r="P2" t="n">
-        <v>1.300946133138182</v>
+        <v>22.61263972484953</v>
       </c>
       <c r="Q2" t="n">
-        <v>159516</v>
+        <v>68904</v>
       </c>
       <c r="R2" t="n">
-        <v>46081</v>
+        <v>8167</v>
       </c>
       <c r="S2" t="n">
-        <v>25.76</v>
+        <v>76.23</v>
       </c>
       <c r="T2" t="n">
-        <v>6.2</v>
+        <v>7.87</v>
       </c>
       <c r="U2" t="n">
-        <v>3.43</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>53.58085403991233</v>
+        <v>75.78395661417136</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17.69876929087712</v>
+        <v>34.39628482972136</v>
       </c>
       <c r="F3" t="n">
-        <v>19.85162445638271</v>
+        <v>44.55927051671733</v>
       </c>
       <c r="G3" t="n">
-        <v>12.22122302158273</v>
+        <v>26.01873536299766</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1168</v>
+        <v>667</v>
       </c>
       <c r="I3" t="n">
-        <v>53.28962129081927</v>
+        <v>35.50477381816852</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6144223693892568</v>
+        <v>0.7938793879387939</v>
       </c>
       <c r="K3" t="n">
-        <v>18.99870072744285</v>
+        <v>76.46921430165466</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>11.1933589020679</v>
+        <v>17.95524410389091</v>
       </c>
       <c r="M3" t="n">
-        <v>35.64606224742226</v>
+        <v>81.11627776293705</v>
       </c>
       <c r="N3" t="n">
-        <v>19.85339817550189</v>
+        <v>29.16686408659448</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.01816761086149639</v>
+        <v>0.01857585139318885</v>
       </c>
       <c r="P3" t="n">
-        <v>67.15000000000001</v>
+        <v>82.73684210526316</v>
       </c>
       <c r="Q3" t="n">
-        <v>22240</v>
+        <v>4270</v>
       </c>
       <c r="R3" t="n">
-        <v>2718</v>
+        <v>1111</v>
       </c>
       <c r="S3" t="n">
-        <v>33.32</v>
+        <v>60.44</v>
       </c>
       <c r="T3" t="n">
-        <v>9.25</v>
+        <v>5.74</v>
       </c>
       <c r="U3" t="n">
-        <v>3.69</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>68.57518067906615</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>117.7544910179641</v>
+      </c>
+      <c r="F4" t="n">
+        <v>157.7476255088195</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.12281708616873</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>2938</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.619579647082308</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.061530638189677</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18.28200866249903</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>14.54857371180267</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22.91342774360596</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14.85231951299384</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.1032934131736527</v>
+      </c>
+      <c r="P4" t="n">
+        <v>41.18620689655172</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>24394</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3933</v>
+      </c>
+      <c r="S4" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="T4" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADANIPOWER</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>68.24419348645391</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>48.27674122146251</v>
+      </c>
+      <c r="F5" t="n">
+        <v>23.44105657077455</v>
+      </c>
+      <c r="G5" t="n">
+        <v>41.36759945184802</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>17651</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30.71118060790721</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6803015027125642</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24.29479715622616</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>16.08609641044097</v>
+      </c>
+      <c r="M5" t="n">
+        <v>154.0708845994445</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.8023177656738903</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8.297225501770956</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>50351</v>
+      </c>
+      <c r="R5" t="n">
+        <v>20829</v>
+      </c>
+      <c r="S5" t="n">
+        <v>44.57</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>65.86887500565507</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>29.67748825288338</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35.77492689368928</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15.6585434568249</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>3556</v>
+      </c>
+      <c r="I6" t="n">
+        <v>18.03587045363451</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.09823677581864</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17.80103767695105</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>13.02966034945308</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20.11756716333324</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20.27736210195506</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.1321016659547202</v>
+      </c>
+      <c r="P6" t="n">
+        <v>41.00487804878049</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>35495</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5558</v>
+      </c>
+      <c r="S6" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>62.33801822894155</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>20.78030212917806</v>
+      </c>
+      <c r="F7" t="n">
+        <v>30.81124132438275</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14.10805136073649</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>955</v>
+      </c>
+      <c r="I7" t="n">
+        <v>23.53017525858574</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.559244419004007</v>
+      </c>
+      <c r="K7" t="n">
+        <v>19.2998469335665</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>11.83637017589811</v>
+      </c>
+      <c r="M7" t="n">
+        <v>15.76701574818362</v>
+      </c>
+      <c r="N7" t="n">
+        <v>13.48774998597666</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.04543832520518615</v>
+      </c>
+      <c r="P7" t="n">
+        <v>54.33333333333334</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>12383</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1747</v>
+      </c>
+      <c r="S7" t="n">
+        <v>36.12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>59.52330621078019</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>36.30776794493609</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33.86016148428105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.93535353535353</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.913337846987136</v>
+      </c>
+      <c r="K8" t="n">
+        <v>68.36335197744833</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>36.30691600183056</v>
+      </c>
+      <c r="N8" t="n">
+        <v>73.11367578503176</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.4309242871189774</v>
+      </c>
+      <c r="P8" t="n">
+        <v>8.043478260869565</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>12375</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1477</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="T8" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>59.39889013890872</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>15.7230643179025</v>
+      </c>
+      <c r="F9" t="n">
+        <v>146.3235294117647</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.366915605017816</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="I9" t="n">
+        <v>32.27903093325808</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.254299114121939</v>
+      </c>
+      <c r="K9" t="n">
+        <v>18.98796206427069</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>12.91184100336258</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.217125634550683</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12.83917371819816</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.002867677181482999</v>
+      </c>
+      <c r="P9" t="n">
+        <v>160.0267857142857</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20487</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1919</v>
+      </c>
+      <c r="S9" t="n">
+        <v>49</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>56.56733689660949</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>15.09416181067115</v>
+      </c>
+      <c r="F10" t="n">
+        <v>19.44697569501501</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19.81565870053818</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>11372</v>
+      </c>
+      <c r="I10" t="n">
+        <v>43.2382586094409</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.262747138397503</v>
+      </c>
+      <c r="K10" t="n">
+        <v>13.12675558948349</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>10.78116321985565</v>
+      </c>
+      <c r="M10" t="n">
+        <v>61.72296197042512</v>
+      </c>
+      <c r="N10" t="n">
+        <v>24.53682964293125</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.05142381453500244</v>
+      </c>
+      <c r="P10" t="n">
+        <v>58.33193277310924</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>48497</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9610</v>
+      </c>
+      <c r="S10" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>55.32776263242075</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>17.99027109750765</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28.8880112339828</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>12547</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-7.360467011220518</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.413207178663658</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21.39660074377121</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>17.25086850260209</v>
+      </c>
+      <c r="M11" t="n">
+        <v>31.28635844345755</v>
+      </c>
+      <c r="N11" t="n">
+        <v>51.94877118224903</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>6.445624336310825</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.300946133138182</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>159516</v>
+      </c>
+      <c r="R11" t="n">
+        <v>46081</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="T11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>55.02230261239121</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>22.17234691050152</v>
+      </c>
+      <c r="F12" t="n">
+        <v>23.44562391681109</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24.19569424286405</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.552520013345259</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9307673081729567</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23.776441520116</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>11.03693649673969</v>
+      </c>
+      <c r="M12" t="n">
+        <v>43.74750602520056</v>
+      </c>
+      <c r="N12" t="n">
+        <v>12.6758416653777</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.02321972845663619</v>
+      </c>
+      <c r="P12" t="n">
+        <v>114.7058823529412</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16536</v>
+      </c>
+      <c r="R12" t="n">
+        <v>4001</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="T12" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>54.04288623497285</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>15.3548827162833</v>
+      </c>
+      <c r="F13" t="n">
+        <v>15.24626398560363</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30.33956048070083</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>8250</v>
+      </c>
+      <c r="I13" t="n">
+        <v>37.78973446864202</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.853158933859822</v>
+      </c>
+      <c r="K13" t="n">
+        <v>28.63193631184944</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>19.57867595245697</v>
+      </c>
+      <c r="M13" t="n">
+        <v>17.08412657928569</v>
+      </c>
+      <c r="N13" t="n">
+        <v>14.90956518204163</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.9373223691689719</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5.949506037321624</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>26711</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8104</v>
+      </c>
+      <c r="S13" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MARUTI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>49.80451323822801</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>15.75038535195478</v>
+      </c>
+      <c r="F14" t="n">
+        <v>21.72001632557868</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.50809964894472</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>4936</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10.02778351575371</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.245625741399763</v>
+      </c>
+      <c r="K14" t="n">
+        <v>26.32364432616601</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>10.51021511264258</v>
+      </c>
+      <c r="M14" t="n">
+        <v>45.38758594934527</v>
+      </c>
+      <c r="N14" t="n">
+        <v>12.00718203930038</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.001389602503619973</v>
+      </c>
+      <c r="P14" t="n">
+        <v>117.9072164948454</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>141858</v>
+      </c>
+      <c r="R14" t="n">
+        <v>13488</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DRREDDY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>49.72199065339081</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>19.74233736816026</v>
+      </c>
+      <c r="F15" t="n">
+        <v>26.21959280803807</v>
+      </c>
+      <c r="G15" t="n">
+        <v>19.9136053693192</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>509</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-24.68901184980715</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.8144496235209753</v>
+      </c>
+      <c r="K15" t="n">
+        <v>13.71726615103832</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>12.63964434957199</v>
+      </c>
+      <c r="M15" t="n">
+        <v>41.90561020689674</v>
+      </c>
+      <c r="N15" t="n">
+        <v>23.39250464543747</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.07085722375592836</v>
+      </c>
+      <c r="P15" t="n">
+        <v>51.70760233918129</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>28011</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5578</v>
+      </c>
+      <c r="S15" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>48.96924437828527</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>50.94431367348518</v>
+      </c>
+      <c r="F16" t="n">
+        <v>65.26850065983149</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19.13671215020777</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>50429</v>
+      </c>
+      <c r="I16" t="n">
+        <v>10.77084245698778</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9617996051975097</v>
+      </c>
+      <c r="K16" t="n">
+        <v>13.63286455550641</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>10.4636148017166</v>
+      </c>
+      <c r="M16" t="n">
+        <v>12.28631019980659</v>
+      </c>
+      <c r="N16" t="n">
+        <v>7.871172131953608</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.0886406082507266</v>
+      </c>
+      <c r="P16" t="n">
+        <v>87.09511568123393</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>240893</v>
+      </c>
+      <c r="R16" t="n">
+        <v>46099</v>
+      </c>
+      <c r="S16" t="n">
+        <v>78.69</v>
+      </c>
+      <c r="T16" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>47.79763009276988</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>22.9043860525527</v>
+      </c>
+      <c r="F17" t="n">
+        <v>28.91484449273394</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.90931103415266</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1752</v>
+      </c>
+      <c r="I17" t="n">
+        <v>22.08444037386408</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.236641221374046</v>
+      </c>
+      <c r="K17" t="n">
+        <v>42.13101535214459</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>30.32798083513346</v>
+      </c>
+      <c r="M17" t="n">
+        <v>33.24835486418234</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24.775129058601</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.1034568888000799</v>
+      </c>
+      <c r="P17" t="n">
+        <v>31.93243243243243</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35517</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4585</v>
+      </c>
+      <c r="S17" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>CANBK</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D18" t="n">
         <v>43.47964522572428</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E18" s="2" t="n">
         <v>16.71605179468811</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F18" t="n">
         <v>3.15654898752525</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G18" t="n">
         <v>13.93516047014541</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H18" s="2" t="n">
         <v>13296</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I18" t="n">
         <v>-5.337862323751841</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J18" t="n">
         <v>0.9769495487306019</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K18" t="n">
         <v>16.30293930023252</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L18" s="2" t="n">
         <v>18.17561078322378</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M18" t="n">
         <v>73.3401622666352</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N18" t="n">
         <v>85.7752850068174</v>
       </c>
-      <c r="O4" s="3" t="n">
+      <c r="O18" s="3" t="n">
         <v>14.86741992554242</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P18" t="n">
         <v>1.610661174334986</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q18" t="n">
         <v>110519</v>
       </c>
-      <c r="R4" t="n">
+      <c r="R18" t="n">
         <v>15401</v>
       </c>
-      <c r="S4" t="n">
+      <c r="S18" t="n">
         <v>36.74</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T18" t="n">
         <v>12.61</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U18" t="n">
         <v>3.81</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>37.19234640450557</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>29.78800671841663</v>
+      </c>
+      <c r="F19" t="n">
+        <v>37.75589530966572</v>
+      </c>
+      <c r="G19" t="n">
+        <v>17.08075746730006</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>20117</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7.201272446841034</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9604541298384639</v>
+      </c>
+      <c r="K19" t="n">
+        <v>15.21650079880636</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>13.19910093055623</v>
+      </c>
+      <c r="M19" t="n">
+        <v>10.55879647674076</v>
+      </c>
+      <c r="N19" t="n">
+        <v>11.23941998365794</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>0.09486358890553362</v>
+      </c>
+      <c r="P19" t="n">
+        <v>87.52340425531915</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>153670</v>
+      </c>
+      <c r="R19" t="n">
+        <v>26248</v>
+      </c>
+      <c r="S19" t="n">
+        <v>35.99</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>36.48952437105826</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>23.01393141233172</v>
+      </c>
+      <c r="F20" t="n">
+        <v>32.69072290295998</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14.29312274253273</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>15840</v>
+      </c>
+      <c r="I20" t="n">
+        <v>22.6161818543015</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.428898790579249</v>
+      </c>
+      <c r="K20" t="n">
+        <v>13.39647732977698</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>12.71029997837341</v>
+      </c>
+      <c r="M20" t="n">
+        <v>12.0436628527816</v>
+      </c>
+      <c r="N20" t="n">
+        <v>9.194090295112023</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>0.08435023365512796</v>
+      </c>
+      <c r="P20" t="n">
+        <v>46.46112115732369</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>109913</v>
+      </c>
+      <c r="R20" t="n">
+        <v>15710</v>
+      </c>
+      <c r="S20" t="n">
+        <v>63.63</v>
+      </c>
+      <c r="T20" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>35.98973436950509</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>17.06727541291795</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24.27096774193548</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6.837009144701453</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-13.35487386941974</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.536585365853659</v>
+      </c>
+      <c r="K21" t="n">
+        <v>21.14089015706202</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>13.03790793906312</v>
+      </c>
+      <c r="M21" t="n">
+        <v>6.77797587953104</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10.03323122942004</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>0.040687525177924</v>
+      </c>
+      <c r="P21" t="n">
+        <v>25.35714285714286</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>18590</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1271</v>
+      </c>
+      <c r="S21" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="T21" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>32.59631594438643</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>77.66510140873214</v>
+      </c>
+      <c r="F22" t="n">
+        <v>135.2030422382181</v>
+      </c>
+      <c r="G22" t="n">
+        <v>7.031246466738726</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>20445</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.174889046118222</v>
+      </c>
+      <c r="K22" t="n">
+        <v>17.59282162428875</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>10.33534798968241</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6.361264204860495</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.75885858017449</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>0.1034568888000799</v>
+      </c>
+      <c r="P22" t="n">
+        <v>3.544154751892346</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>221113</v>
+      </c>
+      <c r="R22" t="n">
+        <v>15547</v>
+      </c>
+      <c r="S22" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>
@@ -810,15 +2073,15 @@
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
     <col width="20" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
     <col width="10" customWidth="1" min="20" max="20"/>
@@ -940,7 +2203,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -949,10 +2212,49 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10.90284920669398</v>
+        <v>37.40050238194505</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11.54654941693749</v>
+      </c>
+      <c r="F2" t="n">
+        <v>20.2313518675261</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.060025128683176</v>
+      </c>
+      <c r="H2" t="n">
+        <v>925</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-1.428567128563307</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.506291390728477</v>
+      </c>
+      <c r="K2" t="n">
+        <v>19.82084189180693</v>
+      </c>
+      <c r="L2" t="n">
+        <v>9.211957132942761</v>
+      </c>
+      <c r="M2" t="n">
+        <v>24.39263468831445</v>
+      </c>
+      <c r="N2" t="n">
+        <v>7.557399109099472</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>0.7788502788502788</v>
+        <v>0.7616899254444657</v>
+      </c>
+      <c r="P2" t="n">
+        <v>5.224737713970182</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>98692</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3020</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>9.539999999999999</v>
@@ -972,7 +2274,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -981,10 +2283,46 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.256607748328325</v>
+        <v>20.67802027565396</v>
+      </c>
+      <c r="E3" t="n">
+        <v>18.53754343556428</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14.23726099166652</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.822387437265419</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-11245</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-0.4588427057864711</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23.2535428740343</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5.838805854237616</v>
+      </c>
+      <c r="M3" t="n">
+        <v>100.9544327543091</v>
+      </c>
+      <c r="N3" t="n">
+        <v>15.31688706104797</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>1.657314686108196</v>
+        <v>1.641441305333132</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3.764690170940171</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>139078</v>
+      </c>
+      <c r="R3" t="n">
+        <v>12270</v>
       </c>
       <c r="S3" s="2" t="n">
         <v>14.22</v>
@@ -1007,7 +2345,3610 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>broad_sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>return_on_equity_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>free_cash_flow_cr</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fcf_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cfo_quality_ratio</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>debt_to_equity</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>91.04945832404229</v>
+      </c>
+      <c r="E2" t="n">
+        <v>892.5683060109289</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5640.87982832618</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.8527226285847</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9424</v>
+      </c>
+      <c r="I2" t="n">
+        <v>71.56520119992503</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.593730868127832</v>
+      </c>
+      <c r="K2" t="n">
+        <v>67.58091776468258</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>19.31335512580617</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>120.6925086746793</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.01857923497267759</v>
+      </c>
+      <c r="P2" t="n">
+        <v>22.61263972484953</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>68904</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8167</v>
+      </c>
+      <c r="S2" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>75.78395661417136</v>
+      </c>
+      <c r="E3" t="n">
+        <v>34.39628482972136</v>
+      </c>
+      <c r="F3" t="n">
+        <v>44.55927051671733</v>
+      </c>
+      <c r="G3" t="n">
+        <v>26.01873536299766</v>
+      </c>
+      <c r="H3" t="n">
+        <v>667</v>
+      </c>
+      <c r="I3" t="n">
+        <v>35.50477381816852</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7938793879387939</v>
+      </c>
+      <c r="K3" t="n">
+        <v>76.46921430165466</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>17.95524410389091</v>
+      </c>
+      <c r="M3" t="n">
+        <v>81.11627776293705</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>29.16686408659448</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.01857585139318885</v>
+      </c>
+      <c r="P3" t="n">
+        <v>82.73684210526316</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>4270</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1111</v>
+      </c>
+      <c r="S3" t="n">
+        <v>60.44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>59.52330621078019</v>
+      </c>
+      <c r="E4" t="n">
+        <v>36.30776794493609</v>
+      </c>
+      <c r="F4" t="n">
+        <v>33.86016148428105</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.93535353535353</v>
+      </c>
+      <c r="H4" t="n">
+        <v>841</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.913337846987136</v>
+      </c>
+      <c r="K4" t="n">
+        <v>68.36335197744833</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>36.30691600183056</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>73.11367578503176</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.4309242871189774</v>
+      </c>
+      <c r="P4" t="n">
+        <v>8.043478260869565</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12375</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1477</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="T4" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ATGL</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>59.18976350842978</v>
+      </c>
+      <c r="E5" t="n">
+        <v>18.65921787709497</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21.49114269028616</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14.92737430167598</v>
+      </c>
+      <c r="K5" t="n">
+        <v>38.18335427451367</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>21.08864867789759</v>
+      </c>
+      <c r="M5" t="n">
+        <v>12.99654305433795</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>23.8762916927858</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.4349162011173184</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.5045045045045</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4475</v>
+      </c>
+      <c r="R5" t="n">
+        <v>668</v>
+      </c>
+      <c r="S5" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>55.39098859950092</v>
+      </c>
+      <c r="E6" t="n">
+        <v>37.2192057915469</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21.23510292524377</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.843630099444054</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1506</v>
+      </c>
+      <c r="I6" t="n">
+        <v>27.55515729109304</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4848398169336384</v>
+      </c>
+      <c r="K6" t="n">
+        <v>33.14221885428872</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>20.89716395312024</v>
+      </c>
+      <c r="M6" t="n">
+        <v>53.11021124836826</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>20.27457629679304</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1.653145959757266</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9.411954765751211</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>51084</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3496</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="T6" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>55.32776263242075</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.99027109750765</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="G7" t="n">
+        <v>28.8880112339828</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12547</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-7.360467011220518</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.413207178663658</v>
+      </c>
+      <c r="K7" t="n">
+        <v>21.39660074377121</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>17.25086850260209</v>
+      </c>
+      <c r="M7" t="n">
+        <v>31.28635844345755</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>51.94877118224903</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>6.445624336310825</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.300946133138182</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>159516</v>
+      </c>
+      <c r="R7" t="n">
+        <v>46081</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="T7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>50.32190665581052</v>
+      </c>
+      <c r="E8" t="n">
+        <v>18.8419213518306</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4.350587230638684</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26.28792839991269</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-79931</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-5.034945678499758</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27.25940575809531</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>24.35264273954201</v>
+      </c>
+      <c r="M8" t="n">
+        <v>48.41981202939976</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>29.32313482597901</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>3.824788776468134</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2689.166666666667</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>54972</v>
+      </c>
+      <c r="R8" t="n">
+        <v>14451</v>
+      </c>
+      <c r="S8" t="n">
+        <v>69.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>47.79763009276988</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22.9043860525527</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28.91484449273394</v>
+      </c>
+      <c r="G9" t="n">
+        <v>12.90931103415266</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1752</v>
+      </c>
+      <c r="I9" t="n">
+        <v>22.08444037386408</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.236641221374046</v>
+      </c>
+      <c r="K9" t="n">
+        <v>42.13101535214459</v>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>30.32798083513346</v>
+      </c>
+      <c r="M9" t="n">
+        <v>33.24835486418234</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>24.775129058601</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.1034568888000799</v>
+      </c>
+      <c r="P9" t="n">
+        <v>31.93243243243243</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>35517</v>
+      </c>
+      <c r="R9" t="n">
+        <v>4585</v>
+      </c>
+      <c r="S9" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DMART</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>45.43103559954291</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13.56294790886726</v>
+      </c>
+      <c r="F10" t="n">
+        <v>21.28564022809746</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.993207190533383</v>
+      </c>
+      <c r="H10" t="n">
+        <v>278</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.082807570977918</v>
+      </c>
+      <c r="K10" t="n">
+        <v>28.1325519519273</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>20.48312440202782</v>
+      </c>
+      <c r="M10" t="n">
+        <v>32.14493416943994</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>22.96698996520703</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.03166114022890149</v>
+      </c>
+      <c r="P10" t="n">
+        <v>73.29310344827586</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>50789</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2536</v>
+      </c>
+      <c r="S10" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.94</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>44.61256141757723</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14.33974005030719</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.887792835880029</v>
+      </c>
+      <c r="G11" t="n">
+        <v>23.07288232992184</v>
+      </c>
+      <c r="H11" t="n">
+        <v>35669</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.2913699844146319</v>
+      </c>
+      <c r="K11" t="n">
+        <v>30.18695614094877</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>21.95098428169122</v>
+      </c>
+      <c r="M11" t="n">
+        <v>27.12356908487252</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>23.86506357287907</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>6.808786667718385</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.400768822479211</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>283649</v>
+      </c>
+      <c r="R11" t="n">
+        <v>65446</v>
+      </c>
+      <c r="S11" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U11" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>43.47964522572428</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.71605179468811</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.15654898752525</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13.93516047014541</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13296</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-5.337862323751841</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9769495487306019</v>
+      </c>
+      <c r="K12" t="n">
+        <v>16.30293930023252</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>18.17561078322378</v>
+      </c>
+      <c r="M12" t="n">
+        <v>73.3401622666352</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>85.7752850068174</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>14.86741992554242</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.610661174334986</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>110519</v>
+      </c>
+      <c r="R12" t="n">
+        <v>15401</v>
+      </c>
+      <c r="S12" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="T12" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>43.23857278716519</v>
+      </c>
+      <c r="E13" t="n">
+        <v>25.85035141227954</v>
+      </c>
+      <c r="F13" t="n">
+        <v>11.70643157982139</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14.12820930948886</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-79634</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-4.403590894517474</v>
+      </c>
+      <c r="K13" t="n">
+        <v>22.13149041552844</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>20.97274568418761</v>
+      </c>
+      <c r="M13" t="n">
+        <v>28.39996432859242</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>23.74781614270227</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>4.789368120938867</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.197130112323319</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>110382</v>
+      </c>
+      <c r="R13" t="n">
+        <v>15595</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>42.45151007145608</v>
+      </c>
+      <c r="E14" t="n">
+        <v>7.566793298872766</v>
+      </c>
+      <c r="F14" t="n">
+        <v>11.69243370533429</v>
+      </c>
+      <c r="G14" t="n">
+        <v>7.990266999868473</v>
+      </c>
+      <c r="H14" t="n">
+        <v>26</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-37.04887150623013</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.594238683127572</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.436125385661253</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>15.96086282879563</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9.319535187362149</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>21.59956338772886</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.21654107242947</v>
+      </c>
+      <c r="P14" t="n">
+        <v>25.32183908045977</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15206</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1215</v>
+      </c>
+      <c r="S14" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>41.67926984799463</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13.0380853616381</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="G15" t="n">
+        <v>24.0645524488647</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7906</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.234248284466625</v>
+      </c>
+      <c r="K15" t="n">
+        <v>19.10193873049559</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>19.06740855567788</v>
+      </c>
+      <c r="M15" t="n">
+        <v>13.23694644929214</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>23.24502393394037</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>8.378352548852153</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.31948659270683</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>26645</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6412</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>36.48899607519155</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.11635033812082</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.304889074344531</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20.33362647026492</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-31359</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-4.203405865657522</v>
+      </c>
+      <c r="K16" t="n">
+        <v>27.82625310142639</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>18.55607005277675</v>
+      </c>
+      <c r="M16" t="n">
+        <v>43.59376752249222</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>23.49387942502037</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>3.994034363699512</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.6766743648960739</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>36388</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7399</v>
+      </c>
+      <c r="S16" t="n">
+        <v>68.53</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>35.62917961740899</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17.45521359669269</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.495209907313654</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17.84689244899024</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-38538</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-10.43362573099415</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25.98553091668698</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>21.93916480497526</v>
+      </c>
+      <c r="M17" t="n">
+        <v>31.00834610809753</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>23.36341725167208</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>6.863420609401317</v>
+      </c>
+      <c r="P17" t="n">
+        <v>21.21176470588235</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>19163</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3420</v>
+      </c>
+      <c r="S17" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>33.24234443131877</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15.7618637908999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.820446985460198</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.93948250956673</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-7559</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.3325030473263024</v>
+      </c>
+      <c r="K18" t="n">
+        <v>16.78883948962531</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>17.47729766589094</v>
+      </c>
+      <c r="M18" t="n">
+        <v>126.679000994827</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>74.50588066551305</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>12.14371872728943</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.896747724261721</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>118379</v>
+      </c>
+      <c r="R18" t="n">
+        <v>18869</v>
+      </c>
+      <c r="S18" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>INDUSINDBK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>32.74059809901026</v>
+      </c>
+      <c r="E19" t="n">
+        <v>14.25227319776422</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3.561786022241473</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19.56369677362945</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-17468</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1.881899441340782</v>
+      </c>
+      <c r="K19" t="n">
+        <v>16.41029009859514</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>15.49561308335803</v>
+      </c>
+      <c r="M19" t="n">
+        <v>46.68046213913497</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>22.07746495394836</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>6.885742949503957</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.879527055815935</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>45748</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8950</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADANIENT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>27.08649496786737</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.534650424813185</v>
+      </c>
+      <c r="F20" t="n">
+        <v>10.89897112639626</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3.458790097592848</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-8455</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.092053973013493</v>
+      </c>
+      <c r="K20" t="n">
+        <v>34.60338228109774</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>19.01541475308124</v>
+      </c>
+      <c r="M20" t="n">
+        <v>47.18200603751725</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>45.81058899665285</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>1.671358378544375</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.749286498353458</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>96421</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3335</v>
+      </c>
+      <c r="S20" t="n">
+        <v>58.87</v>
+      </c>
+      <c r="T20" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_id</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>broad_sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>composite_quality_score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>return_on_equity_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>return_on_capital_employed_pct</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit_margin_pct</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>free_cash_flow_cr</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fcf_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>cfo_quality_ratio</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>revenue_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_3yr</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>pat_cagr_5yr</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>debt_to_equity</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>interest_coverage</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>net_profit</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>pe_ratio</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>pb_ratio</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dividend_yield_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>INDIGO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>91.04945832404229</v>
+      </c>
+      <c r="E2" t="n">
+        <v>892.5683060109289</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5640.87982832618</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.8527226285847</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>9424</v>
+      </c>
+      <c r="I2" t="n">
+        <v>71.56520119992503</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.593730868127832</v>
+      </c>
+      <c r="K2" t="n">
+        <v>67.58091776468258</v>
+      </c>
+      <c r="L2" t="n">
+        <v>19.31335512580617</v>
+      </c>
+      <c r="N2" t="n">
+        <v>120.6925086746793</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01857923497267759</v>
+      </c>
+      <c r="P2" t="n">
+        <v>22.61263972484953</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>68904</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8167</v>
+      </c>
+      <c r="S2" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7.87</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>4.27</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>69.98058268753408</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3816.582914572864</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3027.639751552795</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24.99917711727725</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.083080974325214</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9.909701355201484</v>
+      </c>
+      <c r="L3" t="n">
+        <v>8.712548590236358</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32.85327865470051</v>
+      </c>
+      <c r="N3" t="n">
+        <v>26.48527056305299</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6180904522613065</v>
+      </c>
+      <c r="P3" t="n">
+        <v>270.8837209302326</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>30381</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7595</v>
+      </c>
+      <c r="S3" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>68.57518067906615</v>
+      </c>
+      <c r="E4" t="n">
+        <v>117.7544910179641</v>
+      </c>
+      <c r="F4" t="n">
+        <v>157.7476255088195</v>
+      </c>
+      <c r="G4" t="n">
+        <v>16.12281708616873</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>2938</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6.619579647082308</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.061530638189677</v>
+      </c>
+      <c r="K4" t="n">
+        <v>18.28200866249903</v>
+      </c>
+      <c r="L4" t="n">
+        <v>14.54857371180267</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22.91342774360596</v>
+      </c>
+      <c r="N4" t="n">
+        <v>14.85231951299384</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.1032934131736527</v>
+      </c>
+      <c r="P4" t="n">
+        <v>41.18620689655172</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>24394</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3933</v>
+      </c>
+      <c r="S4" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="T4" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>66.92411860191763</v>
+      </c>
+      <c r="E5" t="n">
+        <v>13.57678765646027</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.876081752900018</v>
+      </c>
+      <c r="G5" t="n">
+        <v>432.7262044653349</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1469</v>
+      </c>
+      <c r="I5" t="n">
+        <v>25.86754704441738</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2635437881873727</v>
+      </c>
+      <c r="K5" t="n">
+        <v>55.00574158769729</v>
+      </c>
+      <c r="L5" t="n">
+        <v>31.61229344896917</v>
+      </c>
+      <c r="M5" t="n">
+        <v>26.31882270649231</v>
+      </c>
+      <c r="N5" t="n">
+        <v>19.2975590637313</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.001161354544951794</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3764.5</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1702</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7365</v>
+      </c>
+      <c r="S5" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="T5" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>3.37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ASIANPAINT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>65.86887500565507</v>
+      </c>
+      <c r="E6" t="n">
+        <v>29.67748825288338</v>
+      </c>
+      <c r="F6" t="n">
+        <v>35.77492689368928</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15.6585434568249</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>3556</v>
+      </c>
+      <c r="I6" t="n">
+        <v>18.03587045363451</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.09823677581864</v>
+      </c>
+      <c r="K6" t="n">
+        <v>17.80103767695105</v>
+      </c>
+      <c r="L6" t="n">
+        <v>13.02966034945308</v>
+      </c>
+      <c r="M6" t="n">
+        <v>20.11756716333324</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20.27736210195506</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1321016659547202</v>
+      </c>
+      <c r="P6" t="n">
+        <v>41.00487804878049</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>35495</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5558</v>
+      </c>
+      <c r="S6" t="n">
+        <v>73.37</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>2.42</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>POWERGRID</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>65.80281547106689</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.87001124549607</v>
+      </c>
+      <c r="F7" t="n">
+        <v>18.90516562075742</v>
+      </c>
+      <c r="G7" t="n">
+        <v>33.97028990249329</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>24176</v>
+      </c>
+      <c r="I7" t="n">
+        <v>39.69769001638159</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.394528992486997</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.965471644662767</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5.510261937513361</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8.967428329021487</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9.189188268434778</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.417345603929039</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.60298643565485</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>45843</v>
+      </c>
+      <c r="R7" t="n">
+        <v>15573</v>
+      </c>
+      <c r="S7" t="n">
+        <v>64.39</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>COALINDIA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>64.94765376747189</v>
+      </c>
+      <c r="E8" t="n">
+        <v>45.16982956605826</v>
+      </c>
+      <c r="F8" t="n">
+        <v>105.7129732333927</v>
+      </c>
+      <c r="G8" t="n">
+        <v>26.25628846856468</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>13617</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.987217411819094</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.4844389734806925</v>
+      </c>
+      <c r="K8" t="n">
+        <v>16.49395652851666</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.402890725901301</v>
+      </c>
+      <c r="M8" t="n">
+        <v>43.28908935217686</v>
+      </c>
+      <c r="N8" t="n">
+        <v>16.43231987118112</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0788468512027076</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11.24178180085755</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>142324</v>
+      </c>
+      <c r="R8" t="n">
+        <v>37369</v>
+      </c>
+      <c r="S8" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>4.38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>60.70616156404152</v>
+      </c>
+      <c r="E9" t="n">
+        <v>26.61418410330778</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28.38958346829047</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17.17851571205706</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>6486</v>
+      </c>
+      <c r="I9" t="n">
+        <v>23.98235048893478</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.8508043591074209</v>
+      </c>
+      <c r="K9" t="n">
+        <v>17.38465261667195</v>
+      </c>
+      <c r="L9" t="n">
+        <v>8.127604751021389</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16.6427815228184</v>
+      </c>
+      <c r="N9" t="n">
+        <v>9.358917170384974</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06601754022512257</v>
+      </c>
+      <c r="P9" t="n">
+        <v>174.4166666666667</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>44870</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7708</v>
+      </c>
+      <c r="S9" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TRENT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>59.52330621078019</v>
+      </c>
+      <c r="E10" t="n">
+        <v>36.30776794493609</v>
+      </c>
+      <c r="F10" t="n">
+        <v>33.86016148428105</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11.93535353535353</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.913337846987136</v>
+      </c>
+      <c r="K10" t="n">
+        <v>68.36335197744833</v>
+      </c>
+      <c r="L10" t="n">
+        <v>36.30691600183056</v>
+      </c>
+      <c r="N10" t="n">
+        <v>73.11367578503176</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.4309242871189774</v>
+      </c>
+      <c r="P10" t="n">
+        <v>8.043478260869565</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>12375</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1477</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ICICIGI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>59.39889013890872</v>
+      </c>
+      <c r="E11" t="n">
+        <v>15.7230643179025</v>
+      </c>
+      <c r="F11" t="n">
+        <v>146.3235294117647</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.366915605017816</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>486</v>
+      </c>
+      <c r="I11" t="n">
+        <v>32.27903093325808</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.254299114121939</v>
+      </c>
+      <c r="K11" t="n">
+        <v>18.98796206427069</v>
+      </c>
+      <c r="L11" t="n">
+        <v>12.91184100336258</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9.217125634550683</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12.83917371819816</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.002867677181482999</v>
+      </c>
+      <c r="P11" t="n">
+        <v>160.0267857142857</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>20487</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1919</v>
+      </c>
+      <c r="S11" t="n">
+        <v>49</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="U11" s="2" t="n">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>56.56733689660949</v>
+      </c>
+      <c r="E12" t="n">
+        <v>15.09416181067115</v>
+      </c>
+      <c r="F12" t="n">
+        <v>19.44697569501501</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19.81565870053818</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>11372</v>
+      </c>
+      <c r="I12" t="n">
+        <v>43.2382586094409</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.262747138397503</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13.12675558948349</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.78116321985565</v>
+      </c>
+      <c r="M12" t="n">
+        <v>61.72296197042512</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24.53682964293125</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05142381453500244</v>
+      </c>
+      <c r="P12" t="n">
+        <v>58.33193277310924</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>48497</v>
+      </c>
+      <c r="R12" t="n">
+        <v>9610</v>
+      </c>
+      <c r="S12" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="U12" s="2" t="n">
+        <v>3.88</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>55.39098859950092</v>
+      </c>
+      <c r="E13" t="n">
+        <v>37.2192057915469</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21.23510292524377</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.843630099444054</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1506</v>
+      </c>
+      <c r="I13" t="n">
+        <v>27.55515729109304</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4848398169336384</v>
+      </c>
+      <c r="K13" t="n">
+        <v>33.14221885428872</v>
+      </c>
+      <c r="L13" t="n">
+        <v>20.89716395312024</v>
+      </c>
+      <c r="M13" t="n">
+        <v>53.11021124836826</v>
+      </c>
+      <c r="N13" t="n">
+        <v>20.27457629679304</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.653145959757266</v>
+      </c>
+      <c r="P13" t="n">
+        <v>9.411954765751211</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>51084</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3496</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10.51</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>55.32776263242075</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.99027109750765</v>
+      </c>
+      <c r="F14" t="n">
+        <v>5.220349505440574</v>
+      </c>
+      <c r="G14" t="n">
+        <v>28.8880112339828</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>12547</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-7.360467011220518</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.413207178663658</v>
+      </c>
+      <c r="K14" t="n">
+        <v>21.39660074377121</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.25086850260209</v>
+      </c>
+      <c r="M14" t="n">
+        <v>31.28635844345755</v>
+      </c>
+      <c r="N14" t="n">
+        <v>51.94877118224903</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6.445624336310825</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.300946133138182</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>159516</v>
+      </c>
+      <c r="R14" t="n">
+        <v>46081</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>55.02230261239121</v>
+      </c>
+      <c r="E15" t="n">
+        <v>22.17234691050152</v>
+      </c>
+      <c r="F15" t="n">
+        <v>23.44562391681109</v>
+      </c>
+      <c r="G15" t="n">
+        <v>24.19569424286405</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.552520013345259</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.9307673081729567</v>
+      </c>
+      <c r="K15" t="n">
+        <v>23.776441520116</v>
+      </c>
+      <c r="L15" t="n">
+        <v>11.03693649673969</v>
+      </c>
+      <c r="M15" t="n">
+        <v>43.74750602520056</v>
+      </c>
+      <c r="N15" t="n">
+        <v>12.6758416653777</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.02321972845663619</v>
+      </c>
+      <c r="P15" t="n">
+        <v>114.7058823529412</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16536</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4001</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="U15" s="2" t="n">
+        <v>4.41</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>54.10224222301945</v>
+      </c>
+      <c r="E16" t="n">
+        <v>49.44710986501021</v>
+      </c>
+      <c r="F16" t="n">
+        <v>39.61352073186944</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.836600998148862</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-48.21728841371581</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6384299540522045</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.981735429882496</v>
+      </c>
+      <c r="L16" t="n">
+        <v>8.15986061977938</v>
+      </c>
+      <c r="M16" t="n">
+        <v>139.6168760853028</v>
+      </c>
+      <c r="N16" t="n">
+        <v>73.17556747076097</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>371.9375</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>845966</v>
+      </c>
+      <c r="R16" t="n">
+        <v>40916</v>
+      </c>
+      <c r="S16" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LTIM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>47.79763009276988</v>
+      </c>
+      <c r="E17" t="n">
+        <v>22.9043860525527</v>
+      </c>
+      <c r="F17" t="n">
+        <v>28.91484449273394</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.90931103415266</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1752</v>
+      </c>
+      <c r="I17" t="n">
+        <v>22.08444037386408</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.236641221374046</v>
+      </c>
+      <c r="K17" t="n">
+        <v>42.13101535214459</v>
+      </c>
+      <c r="L17" t="n">
+        <v>30.32798083513346</v>
+      </c>
+      <c r="M17" t="n">
+        <v>33.24835486418234</v>
+      </c>
+      <c r="N17" t="n">
+        <v>24.775129058601</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.1034568888000799</v>
+      </c>
+      <c r="P17" t="n">
+        <v>31.93243243243243</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>35517</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4585</v>
+      </c>
+      <c r="S17" t="n">
+        <v>64.52</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U17" s="2" t="n">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>45.60278341048131</v>
+      </c>
+      <c r="E18" t="n">
+        <v>20.63992042440318</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17.30975791126167</v>
+      </c>
+      <c r="G18" t="n">
+        <v>14.88611227356968</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1536</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-8.223254104876499</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5032128514056224</v>
+      </c>
+      <c r="K18" t="n">
+        <v>19.843289373664</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6.717165240230294</v>
+      </c>
+      <c r="M18" t="n">
+        <v>72.86912600423906</v>
+      </c>
+      <c r="N18" t="n">
+        <v>9.275930793686072</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.003232758620689655</v>
+      </c>
+      <c r="P18" t="n">
+        <v>71.78431372549019</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>16727</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2490</v>
+      </c>
+      <c r="S18" t="n">
+        <v>58.43</v>
+      </c>
+      <c r="T18" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="U18" s="2" t="n">
+        <v>4.23</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>HDFCBANK</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>44.61256141757723</v>
+      </c>
+      <c r="E19" t="n">
+        <v>14.33974005030719</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.887792835880029</v>
+      </c>
+      <c r="G19" t="n">
+        <v>23.07288232992184</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>35669</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.2913699844146319</v>
+      </c>
+      <c r="K19" t="n">
+        <v>30.18695614094877</v>
+      </c>
+      <c r="L19" t="n">
+        <v>21.95098428169122</v>
+      </c>
+      <c r="M19" t="n">
+        <v>27.12356908487252</v>
+      </c>
+      <c r="N19" t="n">
+        <v>23.86506357287907</v>
+      </c>
+      <c r="O19" t="n">
+        <v>6.808786667718385</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.400768822479211</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>283649</v>
+      </c>
+      <c r="R19" t="n">
+        <v>65446</v>
+      </c>
+      <c r="S19" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SHREECEM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>44.41940182407181</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.370767521615225</v>
+      </c>
+      <c r="F20" t="n">
+        <v>20.20662820340802</v>
+      </c>
+      <c r="G20" t="n">
+        <v>8.445007553238145</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1929</v>
+      </c>
+      <c r="I20" t="n">
+        <v>7.24045892978542</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.93133294864397</v>
+      </c>
+      <c r="K20" t="n">
+        <v>14.80997180241832</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10.32561591555659</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-9.486515671324725</v>
+      </c>
+      <c r="N20" t="n">
+        <v>11.2926552609119</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.07998840747717723</v>
+      </c>
+      <c r="P20" t="n">
+        <v>19.82558139534884</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>20521</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1733</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>44.06601522973264</v>
+      </c>
+      <c r="E21" t="n">
+        <v>6.908270142781061</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.798373432734667</v>
+      </c>
+      <c r="G21" t="n">
+        <v>42.38369379181578</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-13.16733127538306</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9320851688693098</v>
+      </c>
+      <c r="K21" t="n">
+        <v>5.883921200220743</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-5.136730668466605</v>
+      </c>
+      <c r="M21" t="n">
+        <v>35.99602527786225</v>
+      </c>
+      <c r="N21" t="n">
+        <v>15.69706651383664</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.1225938982019223</v>
+      </c>
+      <c r="P21" t="n">
+        <v>7.457865168539326</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>6427</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2724</v>
+      </c>
+      <c r="S21" t="n">
+        <v>46.26</v>
+      </c>
+      <c r="T21" t="n">
+        <v>14.32</v>
+      </c>
+      <c r="U21" s="2" t="n">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>43.47964522572428</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.71605179468811</v>
+      </c>
+      <c r="F22" t="n">
+        <v>3.15654898752525</v>
+      </c>
+      <c r="G22" t="n">
+        <v>13.93516047014541</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>13296</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-5.337862323751841</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9769495487306019</v>
+      </c>
+      <c r="K22" t="n">
+        <v>16.30293930023252</v>
+      </c>
+      <c r="L22" t="n">
+        <v>18.17561078322378</v>
+      </c>
+      <c r="M22" t="n">
+        <v>73.3401622666352</v>
+      </c>
+      <c r="N22" t="n">
+        <v>85.7752850068174</v>
+      </c>
+      <c r="O22" t="n">
+        <v>14.86741992554242</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.610661174334986</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>110519</v>
+      </c>
+      <c r="R22" t="n">
+        <v>15401</v>
+      </c>
+      <c r="S22" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="T22" t="n">
+        <v>12.61</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>3.81</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>42.7567445568189</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13.48039215686275</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19.51259271334257</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4.905818773282963</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="I23" t="n">
+        <v>14.5722412524085</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.053475935828877</v>
+      </c>
+      <c r="K23" t="n">
+        <v>21.75273635187671</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.66004260219314</v>
+      </c>
+      <c r="M23" t="n">
+        <v>89.6838465061924</v>
+      </c>
+      <c r="N23" t="n">
+        <v>36.13077689773863</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.7688869665513264</v>
+      </c>
+      <c r="P23" t="n">
+        <v>5.565701559020044</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>19059</v>
+      </c>
+      <c r="R23" t="n">
+        <v>935</v>
+      </c>
+      <c r="S23" t="n">
+        <v>47.72</v>
+      </c>
+      <c r="T23" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>42.44726176218785</v>
+      </c>
+      <c r="E24" t="n">
+        <v>9.958650553699458</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12.97418225716822</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8.789365557299389</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>45207</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.00946595798532</v>
+      </c>
+      <c r="K24" t="n">
+        <v>24.46173600944801</v>
+      </c>
+      <c r="L24" t="n">
+        <v>9.606097094616972</v>
+      </c>
+      <c r="M24" t="n">
+        <v>13.71449182840923</v>
+      </c>
+      <c r="N24" t="n">
+        <v>14.68063260349559</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.5784524141094746</v>
+      </c>
+      <c r="P24" t="n">
+        <v>7.728912535686478</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>899041</v>
+      </c>
+      <c r="R24" t="n">
+        <v>79020</v>
+      </c>
+      <c r="S24" t="n">
+        <v>58.34</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>41.67926984799463</v>
+      </c>
+      <c r="E25" t="n">
+        <v>13.0380853616381</v>
+      </c>
+      <c r="F25" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="G25" t="n">
+        <v>24.0645524488647</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>7906</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.234248284466625</v>
+      </c>
+      <c r="K25" t="n">
+        <v>19.10193873049559</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.06740855567788</v>
+      </c>
+      <c r="M25" t="n">
+        <v>13.23694644929214</v>
+      </c>
+      <c r="N25" t="n">
+        <v>23.24502393394037</v>
+      </c>
+      <c r="O25" t="n">
+        <v>8.378352548852153</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.31948659270683</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>26645</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6412</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="U25" s="2" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TATAMOTORS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>39.82448487486577</v>
+      </c>
+      <c r="E26" t="n">
+        <v>37.45613415294755</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30.98033093974399</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7.263066074788551</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>45133</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.135221806520577</v>
+      </c>
+      <c r="K26" t="n">
+        <v>20.57936456937097</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.720159538623927</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.263124425916767</v>
+      </c>
+      <c r="P26" t="n">
+        <v>6.530242339274985</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>437928</v>
+      </c>
+      <c r="R26" t="n">
+        <v>31807</v>
+      </c>
+      <c r="S26" t="n">
+        <v>67.06999999999999</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>37.40050238194505</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11.54654941693749</v>
+      </c>
+      <c r="F27" t="n">
+        <v>20.2313518675261</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3.060025128683176</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>925</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.428567128563307</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.506291390728477</v>
+      </c>
+      <c r="K27" t="n">
+        <v>19.82084189180693</v>
+      </c>
+      <c r="L27" t="n">
+        <v>9.211957132942761</v>
+      </c>
+      <c r="M27" t="n">
+        <v>24.39263468831445</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7.557399109099472</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.7616899254444657</v>
+      </c>
+      <c r="P27" t="n">
+        <v>5.224737713970182</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>98692</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3020</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U27" s="2" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>HAVELLS</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>35.98973436950509</v>
+      </c>
+      <c r="E28" t="n">
+        <v>17.06727541291795</v>
+      </c>
+      <c r="F28" t="n">
+        <v>24.27096774193548</v>
+      </c>
+      <c r="G28" t="n">
+        <v>6.837009144701453</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-13.35487386941974</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.536585365853659</v>
+      </c>
+      <c r="K28" t="n">
+        <v>21.14089015706202</v>
+      </c>
+      <c r="L28" t="n">
+        <v>13.03790793906312</v>
+      </c>
+      <c r="M28" t="n">
+        <v>6.77797587953104</v>
+      </c>
+      <c r="N28" t="n">
+        <v>10.03323122942004</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.040687525177924</v>
+      </c>
+      <c r="P28" t="n">
+        <v>25.35714285714286</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>18590</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1271</v>
+      </c>
+      <c r="S28" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="T28" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>JIOFIN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>32.61940935434708</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.153456416595399</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.120397852630671</v>
+      </c>
+      <c r="G29" t="n">
+        <v>86.52291105121293</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>763</v>
+      </c>
+      <c r="J29" t="n">
+        <v>-0.4224299065420561</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>198.8</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1855</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1605</v>
+      </c>
+      <c r="S29" t="n">
+        <v>34.24</v>
+      </c>
+      <c r="T29" t="n">
+        <v>9.91</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DABUR</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Consumer Staples</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>29.53227960933426</v>
+      </c>
+      <c r="E30" t="n">
+        <v>18.35596999797284</v>
+      </c>
+      <c r="F30" t="n">
+        <v>21.36942391594693</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14.60012899064818</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1042</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-10.72050757546945</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.111540585311982</v>
+      </c>
+      <c r="K30" t="n">
+        <v>9.061384362071356</v>
+      </c>
+      <c r="L30" t="n">
+        <v>7.814065037783324</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.231072252692079</v>
+      </c>
+      <c r="N30" t="n">
+        <v>4.604418961155621</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.1383539428339753</v>
+      </c>
+      <c r="P30" t="n">
+        <v>23.24193548387097</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>12404</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1811</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50.95</v>
+      </c>
+      <c r="T30" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1024,8 +5965,8 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="19" customWidth="1" min="13" max="13"/>
     <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
     <col width="8" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
     <col width="10" customWidth="1" min="19" max="19"/>
@@ -1143,7 +6084,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1157,64 +6098,64 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>55.32776263242075</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17.99027109750765</v>
+        <v>59.39889013890872</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>15.7230643179025</v>
       </c>
       <c r="F2" t="n">
-        <v>5.220349505440574</v>
+        <v>146.3235294117647</v>
       </c>
       <c r="G2" t="n">
-        <v>28.8880112339828</v>
+        <v>9.366915605017816</v>
       </c>
       <c r="H2" t="n">
-        <v>12547</v>
+        <v>486</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.360467011220518</v>
+        <v>32.27903093325808</v>
       </c>
       <c r="J2" t="n">
-        <v>3.413207178663658</v>
+        <v>1.254299114121939</v>
       </c>
       <c r="K2" t="n">
-        <v>21.39660074377121</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>17.25086850260209</v>
+        <v>18.98796206427069</v>
+      </c>
+      <c r="L2" t="n">
+        <v>12.91184100336258</v>
       </c>
       <c r="M2" t="n">
-        <v>31.28635844345755</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>51.94877118224903</v>
+        <v>9.217125634550683</v>
+      </c>
+      <c r="N2" t="n">
+        <v>12.83917371819816</v>
       </c>
       <c r="O2" s="3" t="n">
-        <v>6.445624336310825</v>
+        <v>0.002867677181482999</v>
       </c>
       <c r="P2" t="n">
-        <v>1.300946133138182</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>159516</v>
+        <v>160.0267857142857</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>20487</v>
       </c>
       <c r="R2" t="n">
-        <v>46081</v>
+        <v>1919</v>
       </c>
       <c r="S2" t="n">
-        <v>25.76</v>
+        <v>49</v>
       </c>
       <c r="T2" t="n">
-        <v>6.2</v>
+        <v>7.86</v>
       </c>
       <c r="U2" t="n">
-        <v>3.43</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1228,61 +6169,64 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>44.61256141757723</v>
-      </c>
-      <c r="E3" t="n">
-        <v>14.33974005030719</v>
+        <v>55.32776263242075</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>17.99027109750765</v>
       </c>
       <c r="F3" t="n">
-        <v>4.887792835880029</v>
+        <v>5.220349505440574</v>
       </c>
       <c r="G3" t="n">
-        <v>23.07288232992184</v>
+        <v>28.8880112339828</v>
       </c>
       <c r="H3" t="n">
-        <v>35669</v>
+        <v>12547</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-7.360467011220518</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2913699844146319</v>
+        <v>3.413207178663658</v>
       </c>
       <c r="K3" t="n">
-        <v>30.18695614094877</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>21.95098428169122</v>
+        <v>21.39660074377121</v>
+      </c>
+      <c r="L3" t="n">
+        <v>17.25086850260209</v>
       </c>
       <c r="M3" t="n">
-        <v>27.12356908487252</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>23.86506357287907</v>
+        <v>31.28635844345755</v>
+      </c>
+      <c r="N3" t="n">
+        <v>51.94877118224903</v>
       </c>
       <c r="O3" s="3" t="n">
-        <v>6.808786667718385</v>
+        <v>6.445624336310825</v>
       </c>
       <c r="P3" t="n">
-        <v>1.400768822479211</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>283649</v>
+        <v>1.300946133138182</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>159516</v>
       </c>
       <c r="R3" t="n">
-        <v>65446</v>
+        <v>46081</v>
       </c>
       <c r="S3" t="n">
-        <v>49.42</v>
+        <v>25.76</v>
       </c>
       <c r="T3" t="n">
-        <v>4.4</v>
+        <v>6.2</v>
       </c>
       <c r="U3" t="n">
-        <v>4.33</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1296,64 +6240,64 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>43.47964522572428</v>
-      </c>
-      <c r="E4" t="n">
-        <v>16.71605179468811</v>
+        <v>54.10224222301945</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>49.44710986501021</v>
       </c>
       <c r="F4" t="n">
-        <v>3.15654898752525</v>
+        <v>39.61352073186944</v>
       </c>
       <c r="G4" t="n">
-        <v>13.93516047014541</v>
+        <v>4.836600998148862</v>
       </c>
       <c r="H4" t="n">
-        <v>13296</v>
+        <v>853</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.337862323751841</v>
+        <v>-48.21728841371581</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9769495487306019</v>
+        <v>0.6384299540522045</v>
       </c>
       <c r="K4" t="n">
-        <v>16.30293930023252</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>18.17561078322378</v>
+        <v>6.981735429882496</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8.15986061977938</v>
       </c>
       <c r="M4" t="n">
-        <v>73.3401622666352</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>85.7752850068174</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>14.86741992554242</v>
+        <v>139.6168760853028</v>
+      </c>
+      <c r="N4" t="n">
+        <v>73.17556747076097</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.610661174334986</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>110519</v>
+        <v>371.9375</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>845966</v>
       </c>
       <c r="R4" t="n">
-        <v>15401</v>
+        <v>40916</v>
       </c>
       <c r="S4" t="n">
-        <v>36.74</v>
+        <v>30.67</v>
       </c>
       <c r="T4" t="n">
-        <v>12.61</v>
+        <v>8.1</v>
       </c>
       <c r="U4" t="n">
-        <v>3.81</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1367,61 +6311,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33.24234443131877</v>
-      </c>
-      <c r="E5" t="n">
-        <v>15.7618637908999</v>
+        <v>50.32190665581052</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>18.8419213518306</v>
       </c>
       <c r="F5" t="n">
-        <v>2.820446985460198</v>
+        <v>4.350587230638684</v>
       </c>
       <c r="G5" t="n">
-        <v>15.93948250956673</v>
+        <v>26.28792839991269</v>
       </c>
       <c r="H5" t="n">
-        <v>-7559</v>
+        <v>-79931</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3325030473263024</v>
+        <v>-5.034945678499758</v>
       </c>
       <c r="K5" t="n">
-        <v>16.78883948962531</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>17.47729766589094</v>
+        <v>27.25940575809531</v>
+      </c>
+      <c r="L5" t="n">
+        <v>24.35264273954201</v>
       </c>
       <c r="M5" t="n">
-        <v>126.679000994827</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>74.50588066551305</v>
+        <v>48.41981202939976</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29.32313482597901</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>12.14371872728943</v>
+        <v>3.824788776468134</v>
       </c>
       <c r="P5" t="n">
-        <v>1.896747724261721</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>118379</v>
+        <v>2689.166666666667</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>54972</v>
       </c>
       <c r="R5" t="n">
-        <v>18869</v>
+        <v>14451</v>
       </c>
       <c r="S5" t="n">
-        <v>16.89</v>
+        <v>69.2</v>
       </c>
       <c r="T5" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1435,976 +6379,61 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.74059809901026</v>
-      </c>
-      <c r="E6" t="n">
-        <v>14.25227319776422</v>
+        <v>44.61256141757723</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>14.33974005030719</v>
       </c>
       <c r="F6" t="n">
-        <v>3.561786022241473</v>
+        <v>4.887792835880029</v>
       </c>
       <c r="G6" t="n">
-        <v>19.56369677362945</v>
+        <v>23.07288232992184</v>
       </c>
       <c r="H6" t="n">
-        <v>-17468</v>
+        <v>35669</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.881899441340782</v>
+        <v>0.2913699844146319</v>
       </c>
       <c r="K6" t="n">
-        <v>16.41029009859514</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>15.49561308335803</v>
+        <v>30.18695614094877</v>
+      </c>
+      <c r="L6" t="n">
+        <v>21.95098428169122</v>
       </c>
       <c r="M6" t="n">
-        <v>46.68046213913497</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>22.07746495394836</v>
+        <v>27.12356908487252</v>
+      </c>
+      <c r="N6" t="n">
+        <v>23.86506357287907</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>6.885742949503957</v>
+        <v>6.808786667718385</v>
       </c>
       <c r="P6" t="n">
-        <v>1.879527055815935</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>45748</v>
+        <v>1.400768822479211</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>283649</v>
       </c>
       <c r="R6" t="n">
-        <v>8950</v>
+        <v>65446</v>
       </c>
       <c r="S6" t="n">
-        <v>8.99</v>
+        <v>49.42</v>
       </c>
       <c r="T6" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="21" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>company_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>broad_sector</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>return_on_equity_pct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>return_on_capital_employed_pct</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>net_profit_margin_pct</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>free_cash_flow_cr</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>fcf_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>cfo_quality_ratio</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>revenue_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>revenue_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>pat_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>debt_to_equity</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>interest_coverage</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>net_profit</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>pe_ratio</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>pb_ratio</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>55.32776263242075</v>
-      </c>
-      <c r="E2" t="n">
-        <v>17.99027109750765</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.220349505440574</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.8880112339828</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>12547</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-7.360467011220518</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.413207178663658</v>
-      </c>
-      <c r="K2" t="n">
-        <v>21.39660074377121</v>
-      </c>
-      <c r="L2" t="n">
-        <v>17.25086850260209</v>
-      </c>
-      <c r="M2" t="n">
-        <v>31.28635844345755</v>
-      </c>
-      <c r="N2" t="n">
-        <v>51.94877118224903</v>
-      </c>
-      <c r="O2" t="n">
-        <v>6.445624336310825</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.300946133138182</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>159516</v>
-      </c>
-      <c r="R2" t="n">
-        <v>46081</v>
-      </c>
-      <c r="S2" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>53.58085403991233</v>
-      </c>
-      <c r="E3" t="n">
-        <v>17.69876929087712</v>
-      </c>
-      <c r="F3" t="n">
-        <v>19.85162445638271</v>
-      </c>
-      <c r="G3" t="n">
-        <v>12.22122302158273</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>1168</v>
-      </c>
-      <c r="I3" t="n">
-        <v>53.28962129081927</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6144223693892568</v>
-      </c>
-      <c r="K3" t="n">
-        <v>18.99870072744285</v>
-      </c>
-      <c r="L3" t="n">
-        <v>11.1933589020679</v>
-      </c>
-      <c r="M3" t="n">
-        <v>35.64606224742226</v>
-      </c>
-      <c r="N3" t="n">
-        <v>19.85339817550189</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.01816761086149639</v>
-      </c>
-      <c r="P3" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>22240</v>
-      </c>
-      <c r="R3" t="n">
-        <v>2718</v>
-      </c>
-      <c r="S3" t="n">
-        <v>33.32</v>
-      </c>
-      <c r="T3" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>44.61256141757723</v>
-      </c>
-      <c r="E4" t="n">
-        <v>14.33974005030719</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.887792835880029</v>
-      </c>
-      <c r="G4" t="n">
-        <v>23.07288232992184</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>35669</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.2913699844146319</v>
-      </c>
-      <c r="K4" t="n">
-        <v>30.18695614094877</v>
-      </c>
-      <c r="L4" t="n">
-        <v>21.95098428169122</v>
-      </c>
-      <c r="M4" t="n">
-        <v>27.12356908487252</v>
-      </c>
-      <c r="N4" t="n">
-        <v>23.86506357287907</v>
-      </c>
-      <c r="O4" t="n">
-        <v>6.808786667718385</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.400768822479211</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>283649</v>
-      </c>
-      <c r="R4" t="n">
-        <v>65446</v>
-      </c>
-      <c r="S4" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="T4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U4" s="2" t="n">
         <v>4.33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>43.47964522572428</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16.71605179468811</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.15654898752525</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13.93516047014541</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>13296</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-5.337862323751841</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9769495487306019</v>
-      </c>
-      <c r="K5" t="n">
-        <v>16.30293930023252</v>
-      </c>
-      <c r="L5" t="n">
-        <v>18.17561078322378</v>
-      </c>
-      <c r="M5" t="n">
-        <v>73.3401622666352</v>
-      </c>
-      <c r="N5" t="n">
-        <v>85.7752850068174</v>
-      </c>
-      <c r="O5" t="n">
-        <v>14.86741992554242</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.610661174334986</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>110519</v>
-      </c>
-      <c r="R5" t="n">
-        <v>15401</v>
-      </c>
-      <c r="S5" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="T5" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
-    <col width="19" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="8" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="20" customWidth="1" min="21" max="21"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>company_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>broad_sector</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>composite_quality_score</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>return_on_equity_pct</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>return_on_capital_employed_pct</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>net_profit_margin_pct</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>free_cash_flow_cr</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>fcf_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>cfo_quality_ratio</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>revenue_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>revenue_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>pat_cagr_3yr</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>pat_cagr_5yr</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>debt_to_equity</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>interest_coverage</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>net_profit</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>pe_ratio</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>pb_ratio</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dividend_yield_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>55.32776263242075</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>17.99027109750765</v>
-      </c>
-      <c r="F2" t="n">
-        <v>5.220349505440574</v>
-      </c>
-      <c r="G2" t="n">
-        <v>28.8880112339828</v>
-      </c>
-      <c r="H2" t="n">
-        <v>12547</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-7.360467011220518</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.413207178663658</v>
-      </c>
-      <c r="K2" t="n">
-        <v>21.39660074377121</v>
-      </c>
-      <c r="L2" t="n">
-        <v>17.25086850260209</v>
-      </c>
-      <c r="M2" t="n">
-        <v>31.28635844345755</v>
-      </c>
-      <c r="N2" t="n">
-        <v>51.94877118224903</v>
-      </c>
-      <c r="O2" s="3" t="n">
-        <v>6.445624336310825</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.300946133138182</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>159516</v>
-      </c>
-      <c r="R2" t="n">
-        <v>46081</v>
-      </c>
-      <c r="S2" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3.43</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>HDFCBANK</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>44.61256141757723</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>14.33974005030719</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4.887792835880029</v>
-      </c>
-      <c r="G3" t="n">
-        <v>23.07288232992184</v>
-      </c>
-      <c r="H3" t="n">
-        <v>35669</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.2913699844146319</v>
-      </c>
-      <c r="K3" t="n">
-        <v>30.18695614094877</v>
-      </c>
-      <c r="L3" t="n">
-        <v>21.95098428169122</v>
-      </c>
-      <c r="M3" t="n">
-        <v>27.12356908487252</v>
-      </c>
-      <c r="N3" t="n">
-        <v>23.86506357287907</v>
-      </c>
-      <c r="O3" s="3" t="n">
-        <v>6.808786667718385</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.400768822479211</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>283649</v>
-      </c>
-      <c r="R3" t="n">
-        <v>65446</v>
-      </c>
-      <c r="S3" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="T3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="U3" t="n">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>43.69084790902945</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>14.01301818853291</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7.234918028249577</v>
-      </c>
-      <c r="G4" t="n">
-        <v>32.38615146611662</v>
-      </c>
-      <c r="H4" t="n">
-        <v>6766</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.8611980453522209</v>
-      </c>
-      <c r="K4" t="n">
-        <v>19.66335897034557</v>
-      </c>
-      <c r="L4" t="n">
-        <v>13.51960376324537</v>
-      </c>
-      <c r="M4" t="n">
-        <v>22.16271228299323</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20.38200065626572</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>4.003739266919029</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.236375108447038</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>56237</v>
-      </c>
-      <c r="R4" t="n">
-        <v>18213</v>
-      </c>
-      <c r="S4" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>43.47964522572428</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>16.71605179468811</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3.15654898752525</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13.93516047014541</v>
-      </c>
-      <c r="H5" t="n">
-        <v>13296</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-5.337862323751841</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9769495487306019</v>
-      </c>
-      <c r="K5" t="n">
-        <v>16.30293930023252</v>
-      </c>
-      <c r="L5" t="n">
-        <v>18.17561078322378</v>
-      </c>
-      <c r="M5" t="n">
-        <v>73.3401622666352</v>
-      </c>
-      <c r="N5" t="n">
-        <v>85.7752850068174</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>14.86741992554242</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.610661174334986</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>110519</v>
-      </c>
-      <c r="R5" t="n">
-        <v>15401</v>
-      </c>
-      <c r="S5" t="n">
-        <v>36.74</v>
-      </c>
-      <c r="T5" t="n">
-        <v>12.61</v>
-      </c>
-      <c r="U5" t="n">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>37.68910911829928</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>15.83271240518905</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2.612569500628303</v>
-      </c>
-      <c r="G6" t="n">
-        <v>22.73130411725443</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-14556</v>
-      </c>
-      <c r="J6" t="n">
-        <v>-0.2234423394071035</v>
-      </c>
-      <c r="K6" t="n">
-        <v>19.96604689042871</v>
-      </c>
-      <c r="L6" t="n">
-        <v>14.74358712051438</v>
-      </c>
-      <c r="M6" t="n">
-        <v>55.68795030685318</v>
-      </c>
-      <c r="N6" t="n">
-        <v>39.67228711897934</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>8.249122739980766</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.691203992514036</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>109369</v>
-      </c>
-      <c r="R6" t="n">
-        <v>24861</v>
-      </c>
-      <c r="S6" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="T6" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2418,52 +6447,61 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37.64535351516061</v>
+        <v>43.69084790902945</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>61.32056519118731</v>
+        <v>14.01301818853291</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.234918028249577</v>
       </c>
       <c r="G7" t="n">
-        <v>8.395910695456838</v>
+        <v>32.38615146611662</v>
       </c>
       <c r="H7" t="n">
-        <v>-29445</v>
+        <v>6766</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.051108441629355</v>
+        <v>0.8611980453522209</v>
       </c>
       <c r="K7" t="n">
-        <v>10.00319904301221</v>
+        <v>19.66335897034557</v>
       </c>
       <c r="L7" t="n">
-        <v>15.90207600910603</v>
+        <v>13.51960376324537</v>
       </c>
       <c r="M7" t="n">
-        <v>50.33663144357379</v>
+        <v>22.16271228299323</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20.38200065626572</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>3.684256345007701</v>
+        <v>4.003739266919029</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.236375108447038</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>109065</v>
+        <v>56237</v>
       </c>
       <c r="R7" t="n">
-        <v>9157</v>
+        <v>18213</v>
       </c>
       <c r="S7" t="n">
-        <v>19.29</v>
+        <v>32.9</v>
       </c>
       <c r="T7" t="n">
-        <v>10.91</v>
+        <v>1.15</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2477,122 +6515,796 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>33.24234443131877</v>
+        <v>43.47964522572428</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>15.7618637908999</v>
+        <v>16.71605179468811</v>
       </c>
       <c r="F8" t="n">
-        <v>2.820446985460198</v>
+        <v>3.15654898752525</v>
       </c>
       <c r="G8" t="n">
-        <v>15.93948250956673</v>
+        <v>13.93516047014541</v>
       </c>
       <c r="H8" t="n">
-        <v>-7559</v>
+        <v>13296</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-5.337862323751841</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3325030473263024</v>
+        <v>0.9769495487306019</v>
       </c>
       <c r="K8" t="n">
-        <v>16.78883948962531</v>
+        <v>16.30293930023252</v>
       </c>
       <c r="L8" t="n">
-        <v>17.47729766589094</v>
+        <v>18.17561078322378</v>
       </c>
       <c r="M8" t="n">
-        <v>126.679000994827</v>
+        <v>73.3401622666352</v>
       </c>
       <c r="N8" t="n">
-        <v>74.50588066551305</v>
+        <v>85.7752850068174</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>12.14371872728943</v>
+        <v>14.86741992554242</v>
       </c>
       <c r="P8" t="n">
-        <v>1.896747724261721</v>
+        <v>1.610661174334986</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>118379</v>
+        <v>110519</v>
       </c>
       <c r="R8" t="n">
-        <v>18869</v>
+        <v>15401</v>
       </c>
       <c r="S8" t="n">
-        <v>16.89</v>
+        <v>36.74</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>12.61</v>
       </c>
       <c r="U8" t="n">
-        <v>2.62</v>
+        <v>3.81</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>BAJAJFINSV</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>43.23857278716519</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>25.85035141227954</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.70643157982139</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14.12820930948886</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-79634</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-4.403590894517474</v>
+      </c>
+      <c r="K9" t="n">
+        <v>22.13149041552844</v>
+      </c>
+      <c r="L9" t="n">
+        <v>20.97274568418761</v>
+      </c>
+      <c r="M9" t="n">
+        <v>28.39996432859242</v>
+      </c>
+      <c r="N9" t="n">
+        <v>23.74781614270227</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>4.789368120938867</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.197130112323319</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>110382</v>
+      </c>
+      <c r="R9" t="n">
+        <v>15595</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15.07</v>
+      </c>
+      <c r="T9" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SBILIFE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>42.25245356303853</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>12.70458814059566</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.650120740541991</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.434978937479165</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-2099</v>
+      </c>
+      <c r="J10" t="n">
+        <v>15.37592397043295</v>
+      </c>
+      <c r="K10" t="n">
+        <v>17.23587757712</v>
+      </c>
+      <c r="L10" t="n">
+        <v>24.23161418236754</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.162347526806492</v>
+      </c>
+      <c r="N10" t="n">
+        <v>7.374662152227485</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>240.3333333333333</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>131988</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1894</v>
+      </c>
+      <c r="S10" t="n">
+        <v>69.98</v>
+      </c>
+      <c r="T10" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>41.67926984799463</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>13.0380853616381</v>
+      </c>
+      <c r="F11" t="n">
+        <v>5.748474690927067</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24.0645524488647</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7906</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.234248284466625</v>
+      </c>
+      <c r="K11" t="n">
+        <v>19.10193873049559</v>
+      </c>
+      <c r="L11" t="n">
+        <v>19.06740855567788</v>
+      </c>
+      <c r="M11" t="n">
+        <v>13.23694644929214</v>
+      </c>
+      <c r="N11" t="n">
+        <v>23.24502393394037</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>8.378352548852153</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.31948659270683</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>26645</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6412</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PFC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>38.62037150241916</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>26.1609340860332</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3.485901892622635</v>
+      </c>
+      <c r="G12" t="n">
+        <v>28.91659745596014</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-101229</v>
+      </c>
+      <c r="J12" t="n">
+        <v>-3.696761271304939</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.493112204756725</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.08175357755092</v>
+      </c>
+      <c r="M12" t="n">
+        <v>18.9656031749176</v>
+      </c>
+      <c r="N12" t="n">
+        <v>15.92359362270073</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>8.521864217426122</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.5804147544943239</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>91508</v>
+      </c>
+      <c r="R12" t="n">
+        <v>26461</v>
+      </c>
+      <c r="S12" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RECLTD</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>38.05920567548378</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>20.39653929343908</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.29915054435852</v>
+      </c>
+      <c r="G13" t="n">
+        <v>29.7682934528695</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-59554</v>
+      </c>
+      <c r="J13" t="n">
+        <v>-4.080805938494168</v>
+      </c>
+      <c r="K13" t="n">
+        <v>10.14749732259019</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13.33804224786568</v>
+      </c>
+      <c r="M13" t="n">
+        <v>19.07507541943736</v>
+      </c>
+      <c r="N13" t="n">
+        <v>19.76311435023079</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>6.424917087238645</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.600474155202351</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>47517</v>
+      </c>
+      <c r="R13" t="n">
+        <v>14145</v>
+      </c>
+      <c r="S13" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>37.68910911829928</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>15.83271240518905</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.612569500628303</v>
+      </c>
+      <c r="G14" t="n">
+        <v>22.73130411725443</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-14556</v>
+      </c>
+      <c r="J14" t="n">
+        <v>-0.2234423394071035</v>
+      </c>
+      <c r="K14" t="n">
+        <v>19.96604689042871</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14.74358712051438</v>
+      </c>
+      <c r="M14" t="n">
+        <v>55.68795030685318</v>
+      </c>
+      <c r="N14" t="n">
+        <v>39.67228711897934</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>8.249122739980766</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.691203992514036</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>109369</v>
+      </c>
+      <c r="R14" t="n">
+        <v>24861</v>
+      </c>
+      <c r="S14" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PNB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>37.64535351516061</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>61.32056519118731</v>
+      </c>
+      <c r="G15" t="n">
+        <v>8.395910695456838</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-29445</v>
+      </c>
+      <c r="J15" t="n">
+        <v>-3.051108441629355</v>
+      </c>
+      <c r="K15" t="n">
+        <v>10.00319904301221</v>
+      </c>
+      <c r="L15" t="n">
+        <v>15.90207600910603</v>
+      </c>
+      <c r="M15" t="n">
+        <v>50.33663144357379</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>3.684256345007701</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>109065</v>
+      </c>
+      <c r="R15" t="n">
+        <v>9157</v>
+      </c>
+      <c r="S15" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="T15" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SHRIRAMFIN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>36.48899607519155</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>15.11635033812082</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.304889074344531</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20.33362647026492</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-31359</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-4.203405865657522</v>
+      </c>
+      <c r="K16" t="n">
+        <v>27.82625310142639</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18.55607005277675</v>
+      </c>
+      <c r="M16" t="n">
+        <v>43.59376752249222</v>
+      </c>
+      <c r="N16" t="n">
+        <v>23.49387942502037</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>3.994034363699512</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.6766743648960739</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>36388</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7399</v>
+      </c>
+      <c r="S16" t="n">
+        <v>68.53</v>
+      </c>
+      <c r="T16" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.86</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>35.62917961740899</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>17.45521359669269</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3.495209907313654</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17.84689244899024</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-38538</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-10.43362573099415</v>
+      </c>
+      <c r="K17" t="n">
+        <v>25.98553091668698</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.93916480497526</v>
+      </c>
+      <c r="M17" t="n">
+        <v>31.00834610809753</v>
+      </c>
+      <c r="N17" t="n">
+        <v>23.36341725167208</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>6.863420609401317</v>
+      </c>
+      <c r="P17" t="n">
+        <v>21.21176470588235</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>19163</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3420</v>
+      </c>
+      <c r="S17" t="n">
+        <v>16.79</v>
+      </c>
+      <c r="T17" t="n">
+        <v>10.36</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>33.24234443131877</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15.7618637908999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.820446985460198</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.93948250956673</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-7559</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-0.3325030473263024</v>
+      </c>
+      <c r="K18" t="n">
+        <v>16.78883948962531</v>
+      </c>
+      <c r="L18" t="n">
+        <v>17.47729766589094</v>
+      </c>
+      <c r="M18" t="n">
+        <v>126.679000994827</v>
+      </c>
+      <c r="N18" t="n">
+        <v>74.50588066551305</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>12.14371872728943</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.896747724261721</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>118379</v>
+      </c>
+      <c r="R18" t="n">
+        <v>18869</v>
+      </c>
+      <c r="S18" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>INDUSINDBK</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D19" t="n">
         <v>32.74059809901026</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E19" s="2" t="n">
         <v>14.25227319776422</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F19" t="n">
         <v>3.561786022241473</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G19" t="n">
         <v>19.56369677362945</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H19" t="n">
         <v>-17468</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J19" t="n">
         <v>-1.881899441340782</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K19" t="n">
         <v>16.41029009859514</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L19" t="n">
         <v>15.49561308335803</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M19" t="n">
         <v>46.68046213913497</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N19" t="n">
         <v>22.07746495394836</v>
       </c>
-      <c r="O9" s="3" t="n">
+      <c r="O19" s="3" t="n">
         <v>6.885742949503957</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P19" t="n">
         <v>1.879527055815935</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q19" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R19" t="n">
         <v>8950</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S19" t="n">
         <v>8.99</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T19" t="n">
         <v>3.7</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U19" t="n">
         <v>1.42</v>
       </c>
     </row>
